--- a/data/B24_department_schedules_finals/Makine Mühendisliği.xlsx
+++ b/data/B24_department_schedules_finals/Makine Mühendisliği.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\B24_department_schedules_finals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A7EF38-2FF9-4992-9C28-7E93831969F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFC5BDC-0E1B-45B5-9F22-01E689BB4CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/B24_department_schedules_finals/Makine Mühendisliği.xlsx
+++ b/data/B24_department_schedules_finals/Makine Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\B24_department_schedules_finals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBFC5BDC-0E1B-45B5-9F22-01E689BB4CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{92A7EF38-2FF9-4992-9C28-7E93831969F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A29902-E328-41AB-BD35-F398166417FB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>Year:</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>YLAB 2,CAD1,YLAB 2,CAD1</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -373,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -390,11 +393,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -473,18 +483,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}" name="Table1" displayName="Table1" ref="A1:F39" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F39" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}" name="Table1" displayName="Table1" ref="A1:G39" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G39" xr:uid="{625B696F-FBE4-4EF2-8518-810C18A5AFBB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F39">
     <sortCondition ref="C1:C39"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{1FB3D1C1-309C-4BF7-AD72-258A5E23F6F0}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{13BC1CEB-19D3-463C-8CE2-36FD3B265790}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{9221BBC8-E010-48B8-A24D-0C20CC467181}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{449FCC7C-AF42-4141-BCCE-A671718618CA}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{C8015091-4880-4315-B086-0FB0F0D30CC6}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{8D463A4C-1DB6-43F6-9D9C-71FE833DE817}" name="Rooms Used" dataDxfId="0"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{1FB3D1C1-309C-4BF7-AD72-258A5E23F6F0}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{13BC1CEB-19D3-463C-8CE2-36FD3B265790}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9221BBC8-E010-48B8-A24D-0C20CC467181}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{449FCC7C-AF42-4141-BCCE-A671718618CA}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{C8015091-4880-4315-B086-0FB0F0D30CC6}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8D463A4C-1DB6-43F6-9D9C-71FE833DE817}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{CADCC9D6-134A-4FE6-9E2C-36C72E1B262E}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -777,15 +788,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="33.26953125" customWidth="1"/>
-    <col min="6" max="6" width="42.54296875" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="33.265625" customWidth="1"/>
+    <col min="6" max="6" width="42.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -804,8 +815,11 @@
       <c r="F1" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -824,8 +838,12 @@
       <c r="F2" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="7">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -844,8 +862,12 @@
       <c r="F3" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -864,8 +886,12 @@
       <c r="F4" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="7">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -884,8 +910,12 @@
       <c r="F5" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -904,8 +934,11 @@
       <c r="F6" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -924,8 +957,12 @@
       <c r="F7" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="7">
+        <v>5</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -944,8 +981,12 @@
       <c r="F8" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="7">
+        <v>8</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="5">
         <v>4</v>
       </c>
@@ -964,8 +1005,12 @@
       <c r="F9" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="5">
         <v>4</v>
       </c>
@@ -984,8 +1029,12 @@
       <c r="F10" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="7">
+        <v>6</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>1</v>
       </c>
@@ -1004,8 +1053,11 @@
       <c r="F11" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="4">
         <v>3</v>
       </c>
@@ -1024,8 +1076,11 @@
       <c r="F12" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1044,8 +1099,11 @@
       <c r="F13" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -1064,8 +1122,11 @@
       <c r="F14" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -1084,8 +1145,11 @@
       <c r="F15" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -1104,8 +1168,11 @@
       <c r="F16" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="5">
         <v>4</v>
       </c>
@@ -1124,8 +1191,11 @@
       <c r="F17" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="5">
         <v>4</v>
       </c>
@@ -1144,8 +1214,11 @@
       <c r="F18" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="5">
         <v>4</v>
       </c>
@@ -1164,8 +1237,11 @@
       <c r="F19" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -1184,8 +1260,11 @@
       <c r="F20" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="3">
         <v>2</v>
       </c>
@@ -1204,8 +1283,11 @@
       <c r="F21" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1224,8 +1306,11 @@
       <c r="F22" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1244,8 +1329,11 @@
       <c r="F23" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1264,8 +1352,11 @@
       <c r="F24" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>1</v>
       </c>
@@ -1284,8 +1375,11 @@
       <c r="F25" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="3">
         <v>2</v>
       </c>
@@ -1304,8 +1398,11 @@
       <c r="F26" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1324,8 +1421,11 @@
       <c r="F27" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1344,8 +1444,11 @@
       <c r="F28" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>1</v>
       </c>
@@ -1364,8 +1467,11 @@
       <c r="F29" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="3">
         <v>2</v>
       </c>
@@ -1384,8 +1490,11 @@
       <c r="F30" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
         <v>3</v>
       </c>
@@ -1404,8 +1513,11 @@
       <c r="F31" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1424,8 +1536,11 @@
       <c r="F32" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="5">
         <v>4</v>
       </c>
@@ -1444,8 +1559,11 @@
       <c r="F33" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="5">
         <v>4</v>
       </c>
@@ -1464,8 +1582,11 @@
       <c r="F34" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G34" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>1</v>
       </c>
@@ -1484,8 +1605,11 @@
       <c r="F35" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G35" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" s="3">
         <v>2</v>
       </c>
@@ -1504,8 +1628,11 @@
       <c r="F36" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G36" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
         <v>3</v>
       </c>
@@ -1524,8 +1651,11 @@
       <c r="F37" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G37" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" s="5">
         <v>4</v>
       </c>
@@ -1544,8 +1674,11 @@
       <c r="F38" s="5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G38" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" s="5">
         <v>4</v>
       </c>
@@ -1563,6 +1696,9 @@
       </c>
       <c r="F39" s="5" t="s">
         <v>83</v>
+      </c>
+      <c r="G39" s="7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
